--- a/practice/answers/s1_q04.xlsx
+++ b/practice/answers/s1_q04.xlsx
@@ -17,10 +17,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD-MMM-YYYY"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,12 +54,6 @@
       <name val="Consolas"/>
       <color rgb="002F5D46"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -97,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,22 +101,27 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,26 +487,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q4 — Days between deliveries</t>
+          <t>Formatting changes the display, not the value</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Subtracting one date from another gives a number of days, because Excel stores dates as numbers. The result cell must be formatted as a NUMBER -- left as a date it shows a day in January 1900.</t>
+          <t>Column B holds the SAME number in every row -- 0.0842. Only the number format differs. Column D proves the stored value never changed.</t>
         </is>
       </c>
     </row>
@@ -515,137 +514,133 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Format applied</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Crop</t>
+          <t>Displayed as</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Days since previous</t>
+          <t>Number format</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>The formula in C</t>
+          <t>B x 1000</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0.0842</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D5" s="8">
+        <f>B5*1000</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="C6" s="8">
-        <f>A6-A5</f>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Number, 2 decimals</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="D6" s="8">
+        <f>B6*1000</f>
         <v/>
       </c>
-      <c r="D6" s="9">
-        <f>_xlfn.FORMULATEXT(C6)</f>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Percentage, 1 decimal</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D7" s="8">
+        <f>B7*1000</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="C7" s="8">
-        <f>A7-A6</f>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>"$"#,##0.00</t>
+        </is>
+      </c>
+      <c r="D8" s="8">
+        <f>B8*1000</f>
         <v/>
       </c>
-      <c r="D7" s="9">
-        <f>_xlfn.FORMULATEXT(C7)</f>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Scientific</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>0.00E+00</t>
+        </is>
+      </c>
+      <c r="D9" s="8">
+        <f>B9*1000</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="C8" s="8">
-        <f>A8-A7</f>
-        <v/>
-      </c>
-      <c r="D8" s="9">
-        <f>_xlfn.FORMULATEXT(C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-      <c r="C9" s="8">
-        <f>A9-A8</f>
-        <v/>
-      </c>
-      <c r="D9" s="9">
-        <f>_xlfn.FORMULATEXT(C9)</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="18" customHeight="1"/>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>First to last</t>
-        </is>
-      </c>
-      <c r="C11" s="11">
-        <f>A9-A5</f>
-        <v/>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Every row in column D reads 84.20. The percentage row DISPLAYS 8.4% but still holds 0.0842 -- formatting never changes what a formula sees.</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1"/>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>25 days from the first delivery to the last. If a gap shows as a date like 04-Jan-1900, the cell is still formatted as a date -- change it to Number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q04.xlsx
+++ b/practice/answers/s1_q04.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,11 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,39 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -70,12 +40,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,37 +76,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,160 +457,247 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Formatting changes the display, not the value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Column B holds the SAME number in every row -- 0.0842. Only the number format differs. Column D proves the stored value never changed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Format applied</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Displayed as</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Number format</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>B x 1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Protein</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>0.0842</v>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D5" s="8">
-        <f>B5*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Number, 2 decimals</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>0.0842</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="D6" s="8">
-        <f>B6*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Percentage, 1 decimal</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>0.0842</v>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Percentage (2 dp)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Premium?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="C2" s="4">
+        <f>B2</f>
+        <v/>
+      </c>
+      <c r="D2" s="5">
+        <f>B2</f>
+        <v/>
+      </c>
+      <c r="E2" s="6">
+        <f>IF(B2&gt;0.135,"Yes","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="C3" s="4">
+        <f>B3</f>
+        <v/>
+      </c>
+      <c r="D3" s="5">
+        <f>B3</f>
+        <v/>
+      </c>
+      <c r="E3" s="6">
+        <f>IF(B3&gt;0.135,"Yes","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1401</v>
+      </c>
+      <c r="C4" s="4">
+        <f>B4</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>B4</f>
+        <v/>
+      </c>
+      <c r="E4" s="6">
+        <f>IF(B4&gt;0.135,"Yes","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="C5" s="4">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="E5" s="6">
+        <f>IF(B5&gt;0.135,"Yes","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="C6" s="4">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="D6" s="5">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="E6" s="6">
+        <f>IF(B6&gt;0.135,"Yes","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="7">
+        <f>AVERAGE(C2:C6)</f>
+        <v/>
       </c>
       <c r="D7" s="8">
-        <f>B7*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="n">
-        <v>0.0842</v>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>"$"#,##0.00</t>
-        </is>
-      </c>
-      <c r="D8" s="8">
-        <f>B8*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Scientific</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
-        <v>0.0842</v>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>0.00E+00</t>
-        </is>
-      </c>
-      <c r="D9" s="8">
-        <f>B9*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1"/>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Every row in column D reads 84.20. The percentage row DISPLAYS 8.4% but still holds 0.0842 -- formatting never changes what a formula sees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1"/>
+        <f>AVERAGE(D2:D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Value to 4 dp</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>ROUND(C7,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Loads above 13.5%</t>
+        </is>
+      </c>
+      <c r="B10" s="6">
+        <f>COUNTIF(E2:E6,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>The cells hold proportions (0.1342, not 13.42), so nothing is above 13.5 and every row returns No. Formatting a cell as a percentage changes the display, not the stored value.</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:D11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A12:G13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q04.xlsx
+++ b/practice/answers/s1_q04.xlsx
@@ -1,66 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_884D7FDFD678FC3FE566CC7654148E7B9D70F17A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B695BE3-E81A-463E-A828-2C6A1116AF56}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>Protein</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Percentage (2 dp)</t>
+  </si>
+  <si>
+    <t>Premium?</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Value to 4 dp</t>
+  </si>
+  <si>
+    <t>Loads above 13.5%</t>
+  </si>
+  <si>
+    <t>The cells hold proportions (0.1342, not 13.42), so nothing is above 13.5 and every row returns No. Formatting a cell as a percentage changes the display, not the stored value.</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+  <si>
+    <t>Part (e)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
+        <fgColor rgb="FFD9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,95 +153,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -452,247 +471,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="7" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Load</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Protein</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Percentage (2 dp)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Premium?</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.1342</v>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>0.13420000000000001</v>
       </c>
       <c r="C2" s="4">
         <f>B2</f>
-        <v/>
+        <v>0.13420000000000001</v>
       </c>
       <c r="D2" s="5">
         <f>B2</f>
-        <v/>
-      </c>
-      <c r="E2" s="6">
+        <v>0.13420000000000001</v>
+      </c>
+      <c r="E2" s="6" t="str">
         <f>IF(B2&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <v>0.1285</v>
       </c>
       <c r="C3" s="4">
         <f>B3</f>
-        <v/>
+        <v>0.1285</v>
       </c>
       <c r="D3" s="5">
         <f>B3</f>
-        <v/>
-      </c>
-      <c r="E3" s="6">
+        <v>0.1285</v>
+      </c>
+      <c r="E3" s="6" t="str">
         <f>IF(B3&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
         <v>0.1401</v>
       </c>
       <c r="C4" s="4">
         <f>B4</f>
-        <v/>
+        <v>0.1401</v>
       </c>
       <c r="D4" s="5">
         <f>B4</f>
-        <v/>
-      </c>
-      <c r="E4" s="6">
+        <v>0.1401</v>
+      </c>
+      <c r="E4" s="6" t="str">
         <f>IF(B4&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>0.1198</v>
       </c>
       <c r="C5" s="4">
         <f>B5</f>
-        <v/>
+        <v>0.1198</v>
       </c>
       <c r="D5" s="5">
         <f>B5</f>
-        <v/>
-      </c>
-      <c r="E5" s="6">
+        <v>0.1198</v>
+      </c>
+      <c r="E5" s="6" t="str">
         <f>IF(B5&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>0.1356</v>
       </c>
       <c r="C6" s="4">
         <f>B6</f>
-        <v/>
+        <v>0.1356</v>
       </c>
       <c r="D6" s="5">
         <f>B6</f>
-        <v/>
-      </c>
-      <c r="E6" s="6">
+        <v>0.1356</v>
+      </c>
+      <c r="E6" s="6" t="str">
         <f>IF(B6&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="C7" s="7">
         <f>AVERAGE(C2:C6)</f>
-        <v/>
+        <v>0.13164000000000003</v>
       </c>
       <c r="D7" s="8">
         <f>AVERAGE(D2:D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Value to 4 dp</t>
-        </is>
+        <v>0.13164000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="B9" s="10">
         <f>ROUND(C7,4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Loads above 13.5%</t>
-        </is>
+        <v>0.13159999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="B10" s="6">
         <f>COUNTIF(E2:E6,"Yes")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>The cells hold proportions (0.1342, not 13.42), so nothing is above 13.5 and every row returns No. Formatting a cell as a percentage changes the display, not the stored value.</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
-        </is>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="11" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/practice/answers/s1_q04.xlsx
+++ b/practice/answers/s1_q04.xlsx
@@ -1,143 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_884D7FDFD678FC3FE566CC7654148E7B9D70F17A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B695BE3-E81A-463E-A828-2C6A1116AF56}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>Load</t>
-  </si>
-  <si>
-    <t>Protein</t>
-  </si>
-  <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>Percentage (2 dp)</t>
-  </si>
-  <si>
-    <t>Premium?</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Value to 4 dp</t>
-  </si>
-  <si>
-    <t>Loads above 13.5%</t>
-  </si>
-  <si>
-    <t>The cells hold proportions (0.1342, not 13.42), so nothing is above 13.5 and every row returns No. Formatting a cell as a percentage changes the display, not the stored value.</t>
-  </si>
-  <si>
-    <t>Part (a)</t>
-  </si>
-  <si>
-    <t>Part (b)</t>
-  </si>
-  <si>
-    <t>Part (c)</t>
-  </si>
-  <si>
-    <t>Part (d)</t>
-  </si>
-  <si>
-    <t>Part (e)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFE2F3"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D2E9"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -153,37 +69,91 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -471,209 +441,203 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="7" width="11" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>0.13420000000000001</v>
-      </c>
-      <c r="C2" s="4">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Protein (General)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Protein (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Premium? (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="C2" s="2">
         <f>B2</f>
-        <v>0.13420000000000001</v>
-      </c>
-      <c r="D2" s="5">
-        <f>B2</f>
-        <v>0.13420000000000001</v>
-      </c>
-      <c r="E2" s="6" t="str">
+        <v/>
+      </c>
+      <c r="D2" s="3">
         <f>IF(B2&gt;0.135,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>0.1285</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <f>B3</f>
-        <v>0.1285</v>
-      </c>
-      <c r="D3" s="5">
-        <f>B3</f>
-        <v>0.1285</v>
-      </c>
-      <c r="E3" s="6" t="str">
+        <v/>
+      </c>
+      <c r="D3" s="3">
         <f>IF(B3&gt;0.135,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.1401</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <f>B4</f>
-        <v>0.1401</v>
-      </c>
-      <c r="D4" s="5">
-        <f>B4</f>
-        <v>0.1401</v>
-      </c>
-      <c r="E4" s="6" t="str">
+        <v/>
+      </c>
+      <c r="D4" s="3">
         <f>IF(B4&gt;0.135,"Yes","No")</f>
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>0.1198</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <f>B5</f>
-        <v>0.1198</v>
-      </c>
-      <c r="D5" s="5">
-        <f>B5</f>
-        <v>0.1198</v>
-      </c>
-      <c r="E5" s="6" t="str">
+        <v/>
+      </c>
+      <c r="D5" s="3">
         <f>IF(B5&gt;0.135,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>0.1356</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <f>B6</f>
-        <v>0.1356</v>
-      </c>
-      <c r="D6" s="5">
-        <f>B6</f>
-        <v>0.1356</v>
-      </c>
-      <c r="E6" s="6" t="str">
+        <v/>
+      </c>
+      <c r="D6" s="3">
         <f>IF(B6&gt;0.135,"Yes","No")</f>
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="C7" s="7">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Average (b):</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <f>AVERAGE(B2:B6)</f>
+        <v/>
+      </c>
+      <c r="C8" s="5">
         <f>AVERAGE(C2:C6)</f>
-        <v>0.13164000000000003</v>
-      </c>
-      <c r="D7" s="8">
-        <f>AVERAGE(D2:D6)</f>
-        <v>0.13164000000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="10">
-        <f>ROUND(C7,4)</f>
-        <v>0.13159999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6">
-        <f>COUNTIF(E2:E6,"Yes")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="11" t="s">
-        <v>17</v>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Loads above 13.5% (c):</t>
+        </is>
+      </c>
+      <c r="D9" s="3">
+        <f>COUNTIF(D2:D6,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>(d) The stored values are proportions -- 0.1342, not 13.42. The percentage format only changes how the number is displayed. Comparing against 13.5 would ask whether 0.1342 is greater than 13.5, which is never true, so every load would read No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Legend: colours mark question parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:G13"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q04.xlsx
+++ b/practice/answers/s1_q04.xlsx
@@ -593,7 +593,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="64" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>(d) The stored values are proportions -- 0.1342, not 13.42. The percentage format only changes how the number is displayed. Comparing against 13.5 would ask whether 0.1342 is greater than 13.5, which is never true, so every load would read No.</t>

--- a/practice/answers/s1_q04.xlsx
+++ b/practice/answers/s1_q04.xlsx
@@ -486,9 +486,8 @@
       <c r="B2" t="n">
         <v>0.1342</v>
       </c>
-      <c r="C2" s="2">
-        <f>B2</f>
-        <v/>
+      <c r="C2" s="2" t="n">
+        <v>0.1342</v>
       </c>
       <c r="D2" s="3">
         <f>IF(B2&gt;0.135,"Yes","No")</f>
@@ -504,9 +503,8 @@
       <c r="B3" t="n">
         <v>0.1285</v>
       </c>
-      <c r="C3" s="2">
-        <f>B3</f>
-        <v/>
+      <c r="C3" s="2" t="n">
+        <v>0.1285</v>
       </c>
       <c r="D3" s="3">
         <f>IF(B3&gt;0.135,"Yes","No")</f>
@@ -522,9 +520,8 @@
       <c r="B4" t="n">
         <v>0.1401</v>
       </c>
-      <c r="C4" s="2">
-        <f>B4</f>
-        <v/>
+      <c r="C4" s="2" t="n">
+        <v>0.1401</v>
       </c>
       <c r="D4" s="3">
         <f>IF(B4&gt;0.135,"Yes","No")</f>
@@ -540,9 +537,8 @@
       <c r="B5" t="n">
         <v>0.1198</v>
       </c>
-      <c r="C5" s="2">
-        <f>B5</f>
-        <v/>
+      <c r="C5" s="2" t="n">
+        <v>0.1198</v>
       </c>
       <c r="D5" s="3">
         <f>IF(B5&gt;0.135,"Yes","No")</f>
@@ -558,9 +554,8 @@
       <c r="B6" t="n">
         <v>0.1356</v>
       </c>
-      <c r="C6" s="2">
-        <f>B6</f>
-        <v/>
+      <c r="C6" s="2" t="n">
+        <v>0.1356</v>
       </c>
       <c r="D6" s="3">
         <f>IF(B6&gt;0.135,"Yes","No")</f>

--- a/practice/answers/s1_q04.xlsx
+++ b/practice/answers/s1_q04.xlsx
@@ -1,59 +1,132 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_884D98279055962F6F6FF4775FBCEEF89E94F48E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>Protein (General)</t>
+  </si>
+  <si>
+    <t>Protein (%)</t>
+  </si>
+  <si>
+    <t>Premium? (c)</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Average (b):</t>
+  </si>
+  <si>
+    <t>Loads above 13.5% (c):</t>
+  </si>
+  <si>
+    <t>(d) The stored values are proportions -- 0.1342, not 13.42. The percentage format only changes how the number is displayed. Comparing against 13.5 would ask whether 0.1342 is greater than 13.5, which is never true, so every load would read No.</t>
+  </si>
+  <si>
+    <t>Legend: colours mark question parts</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,91 +142,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -441,193 +456,159 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Load</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Protein (General)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Protein (%)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Premium? (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.1342</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.1342</v>
-      </c>
-      <c r="D2" s="3">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.13420000000000001</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.13420000000000001</v>
+      </c>
+      <c r="D2" s="3" t="str">
         <f>IF(B2&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>0.1285</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2">
         <v>0.1285</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="3" t="str">
         <f>IF(B3&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>0.1401</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="2">
         <v>0.1401</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="3" t="str">
         <f>IF(B4&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
         <v>0.1198</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="2">
         <v>0.1198</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="3" t="str">
         <f>IF(B5&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>0.1356</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="2">
         <v>0.1356</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="3" t="str">
         <f>IF(B6&gt;0.135,"Yes","No")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Average (b):</t>
-        </is>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>AVERAGE(B2:B6)</f>
-        <v/>
+        <v>0.13164000000000003</v>
       </c>
       <c r="C8" s="5">
         <f>AVERAGE(C2:C6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Loads above 13.5% (c):</t>
-        </is>
+        <v>0.13164000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D9" s="3">
         <f>COUNTIF(D2:D6,"Yes")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>(d) The stored values are proportions -- 0.1342, not 13.42. The percentage format only changes how the number is displayed. Comparing against 13.5 would ask whether 0.1342 is greater than 13.5, which is never true, so every load would read No.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Legend: colours mark question parts</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="63.95" customHeight="1">
+      <c r="A11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
